--- a/doc/help_dialogs/Input_files/eventsliders.xlsx
+++ b/doc/help_dialogs/Input_files/eventsliders.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="302">
   <si>
     <t xml:space="preserve">EVENT CUSTOM SLIDERS</t>
   </si>
@@ -704,6 +704,12 @@
   </si>
   <si>
     <t xml:space="preserve">sets the p-i-d parameters of the PID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pidWeights(&lt;beta&gt;,&lt;gamma&gt;)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sets the beta and gamma parameters of the PID</t>
   </si>
   <si>
     <t xml:space="preserve">adjustSV(&lt;float&gt;)</t>
@@ -1468,7 +1474,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D146"/>
+  <dimension ref="A1:D147"/>
   <sheetFormatPr defaultColWidth="9.09375" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.09"/>
@@ -2378,7 +2384,6 @@
       <c r="C111" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="D111" s="1"/>
     </row>
     <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B112" s="2" t="s">
@@ -2387,6 +2392,7 @@
       <c r="C112" s="1" t="s">
         <v>236</v>
       </c>
+      <c r="D112" s="1"/>
     </row>
     <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B113" s="2" t="s">
@@ -2509,17 +2515,17 @@
       </c>
     </row>
     <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="1" t="s">
+      <c r="B128" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="B128" s="2" t="s">
+      <c r="C128" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="C128" s="1" t="s">
+    </row>
+    <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="1" t="s">
         <v>269</v>
       </c>
-    </row>
-    <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B129" s="2" t="s">
         <v>270</v>
       </c>
@@ -2577,15 +2583,15 @@
     </row>
     <row r="136" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B136" s="2" t="s">
-        <v>101</v>
+        <v>284</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B137" s="2" t="s">
-        <v>285</v>
+        <v>101</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>286</v>
@@ -2601,26 +2607,26 @@
     </row>
     <row r="139" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B139" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B140" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="C139" s="1" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="B140" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="1" t="s">
+        <v>292</v>
+      </c>
       <c r="B141" s="2" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>293</v>
@@ -2628,45 +2634,53 @@
     </row>
     <row r="142" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B142" s="2" t="s">
-        <v>272</v>
+        <v>294</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="1" t="s">
-        <v>295</v>
-      </c>
       <c r="B143" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="C143" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="C143" s="1" t="s">
+    </row>
+    <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="1" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B144" s="2" t="s">
-        <v>34</v>
+        <v>298</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>118</v>
+        <v>299</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B145" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>164</v>
+        <v>118</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B146" s="2" t="s">
-        <v>298</v>
+        <v>36</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>299</v>
+        <v>164</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B147" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>301</v>
       </c>
     </row>
   </sheetData>

--- a/doc/help_dialogs/Input_files/eventsliders.xlsx
+++ b/doc/help_dialogs/Input_files/eventsliders.xlsx
@@ -805,7 +805,7 @@
     <t xml:space="preserve">playbackmode(&lt;int&gt;)</t>
   </si>
   <si>
-    <t xml:space="preserve">sets playback mode to 0: off, 1: time, 2: BT, 3: ET</t>
+    <t xml:space="preserve">sets playback mode to 0: off, 1: time, 2: BT, 3: ET; 4: BT/time; 5: ET/time</t>
   </si>
   <si>
     <t xml:space="preserve">playbackdropmode(&lt;int&gt;)</t>
@@ -889,37 +889,7 @@
     <t xml:space="preserve">slider(n,&lt;bool&gt;)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">show/hide slider per event type </t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">n</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve"> from {1,2,3,4}</t>
-    </r>
+    <t xml:space="preserve">show/hide slider per event type n from {1,2,3,4}; n=5 toggles the PID SV slider visibility</t>
   </si>
   <si>
     <t xml:space="preserve">quantifier(n,&lt;bool&gt;)</t>

--- a/doc/help_dialogs/Input_files/eventsliders.xlsx
+++ b/doc/help_dialogs/Input_files/eventsliders.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="306">
   <si>
     <t xml:space="preserve">EVENT CUSTOM SLIDERS</t>
   </si>
@@ -563,6 +563,12 @@
     <t xml:space="preserve">sends &lt;value&gt; to &lt;target&gt; via the Kaleido Serial or Network protocol</t>
   </si>
   <si>
+    <t xml:space="preserve">orbiter(&lt;cmd&gt;[,&lt;value&gt;[,&lt;param&gt;]])</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sends &lt;cmd&gt; (1byte in HEX) and optional &lt;value&gt; (0-65535) and &lt;param&gt; (0-255) to Orbiter</t>
+  </si>
+  <si>
     <t xml:space="preserve">shellyrelay(n,b)</t>
   </si>
   <si>
@@ -728,6 +734,12 @@
   </si>
   <si>
     <t xml:space="preserve">sets the PID target set value SV given in C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pidSVbuttons(&lt;bool&gt;)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">toggles the visibility of the PID SV buttons</t>
   </si>
   <si>
     <t xml:space="preserve">pidRS(&lt;rs&gt;)</t>
@@ -1444,7 +1456,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D147"/>
+  <dimension ref="A1:D149"/>
   <sheetFormatPr defaultColWidth="9.09375" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.09"/>
@@ -2030,35 +2042,35 @@
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="1" t="s">
+      <c r="B72" s="2" t="s">
         <v>162</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="1" t="s">
+        <v>164</v>
+      </c>
       <c r="B73" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>118</v>
+        <v>165</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B74" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>164</v>
+        <v>118</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B75" s="2" t="s">
-        <v>165</v>
+        <v>36</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>166</v>
@@ -2105,42 +2117,42 @@
       </c>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="1" t="s">
+      <c r="B81" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B81" s="2"/>
       <c r="C81" s="1" t="s">
-        <v>78</v>
+        <v>178</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B82" s="2"/>
       <c r="C82" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B83" s="2"/>
       <c r="C83" s="1" t="s">
-        <v>180</v>
+        <v>80</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
         <v>181</v>
       </c>
+      <c r="B84" s="2"/>
       <c r="C84" s="1" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B85" s="2" t="s">
+      <c r="A85" s="1" t="s">
         <v>183</v>
       </c>
       <c r="C85" s="1" t="s">
@@ -2165,18 +2177,18 @@
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B88" s="2" t="s">
-        <v>34</v>
+        <v>189</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>118</v>
+        <v>190</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B89" s="2" t="s">
-        <v>189</v>
+        <v>34</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>190</v>
+        <v>118</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2362,7 +2374,6 @@
       <c r="C112" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="D112" s="1"/>
     </row>
     <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B113" s="2" t="s">
@@ -2379,6 +2390,7 @@
       <c r="C114" s="1" t="s">
         <v>240</v>
       </c>
+      <c r="D114" s="1"/>
     </row>
     <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B115" s="2" t="s">
@@ -2493,25 +2505,25 @@
       </c>
     </row>
     <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="1" t="s">
+      <c r="B129" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="B129" s="2" t="s">
+      <c r="C129" s="1" t="s">
         <v>270</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B130" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C130" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="C130" s="1" t="s">
+    </row>
+    <row r="131" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="1" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="131" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B131" s="2" t="s">
         <v>274</v>
       </c>
@@ -2561,23 +2573,23 @@
     </row>
     <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B137" s="2" t="s">
-        <v>101</v>
+        <v>286</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B138" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B139" s="2" t="s">
-        <v>289</v>
+        <v>101</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>290</v>
@@ -2585,43 +2597,40 @@
     </row>
     <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B140" s="2" t="s">
-        <v>110</v>
+        <v>291</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="1" t="s">
-        <v>292</v>
-      </c>
       <c r="B141" s="2" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B142" s="2" t="s">
-        <v>294</v>
+        <v>110</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="1" t="s">
+        <v>296</v>
+      </c>
       <c r="B143" s="2" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="1" t="s">
-        <v>297</v>
-      </c>
       <c r="B144" s="2" t="s">
         <v>298</v>
       </c>
@@ -2631,26 +2640,45 @@
     </row>
     <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B145" s="2" t="s">
-        <v>34</v>
+        <v>278</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>118</v>
+        <v>300</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="1" t="s">
+        <v>301</v>
+      </c>
       <c r="B146" s="2" t="s">
-        <v>36</v>
+        <v>302</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>164</v>
+        <v>303</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B147" s="2" t="s">
-        <v>300</v>
+        <v>34</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>301</v>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B148" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B149" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>305</v>
       </c>
     </row>
   </sheetData>

--- a/doc/help_dialogs/Input_files/eventsliders.xlsx
+++ b/doc/help_dialogs/Input_files/eventsliders.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="308">
   <si>
     <t xml:space="preserve">EVENT CUSTOM SLIDERS</t>
   </si>
@@ -573,6 +573,12 @@
   </si>
   <si>
     <t xml:space="preserve">switches Shelly plug number &lt;n&gt; ON if b is true or 1, and OFF otherwise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">publish(&lt;topic&gt;, &lt;value&gt;)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">converts the given data to JSON and publishes it on the MQTT server to the given topic</t>
   </si>
   <si>
     <t xml:space="preserve">S7 Command</t>
@@ -1456,7 +1462,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D149"/>
+  <dimension ref="A1:D150"/>
   <sheetFormatPr defaultColWidth="9.09375" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.09"/>
@@ -2050,35 +2056,35 @@
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="1" t="s">
+      <c r="B73" s="2" t="s">
         <v>164</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="1" t="s">
+        <v>166</v>
+      </c>
       <c r="B74" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>118</v>
+        <v>167</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B75" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>166</v>
+        <v>118</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B76" s="2" t="s">
-        <v>167</v>
+        <v>36</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>168</v>
@@ -2125,42 +2131,42 @@
       </c>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="1" t="s">
+      <c r="B82" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B82" s="2"/>
       <c r="C82" s="1" t="s">
-        <v>78</v>
+        <v>180</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B83" s="2"/>
       <c r="C83" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B84" s="2"/>
       <c r="C84" s="1" t="s">
-        <v>182</v>
+        <v>80</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
         <v>183</v>
       </c>
+      <c r="B85" s="2"/>
       <c r="C85" s="1" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B86" s="2" t="s">
+      <c r="A86" s="1" t="s">
         <v>185</v>
       </c>
       <c r="C86" s="1" t="s">
@@ -2185,18 +2191,18 @@
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B89" s="2" t="s">
-        <v>34</v>
+        <v>191</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>118</v>
+        <v>192</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B90" s="2" t="s">
-        <v>191</v>
+        <v>34</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>192</v>
+        <v>118</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2390,7 +2396,6 @@
       <c r="C114" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="D114" s="1"/>
     </row>
     <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B115" s="2" t="s">
@@ -2399,6 +2404,7 @@
       <c r="C115" s="1" t="s">
         <v>242</v>
       </c>
+      <c r="D115" s="1"/>
     </row>
     <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B116" s="2" t="s">
@@ -2521,17 +2527,17 @@
       </c>
     </row>
     <row r="131" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="1" t="s">
+      <c r="B131" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="B131" s="2" t="s">
+      <c r="C131" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="C131" s="1" t="s">
+    </row>
+    <row r="132" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="1" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="132" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B132" s="2" t="s">
         <v>276</v>
       </c>
@@ -2589,15 +2595,15 @@
     </row>
     <row r="139" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B139" s="2" t="s">
-        <v>101</v>
+        <v>290</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B140" s="2" t="s">
-        <v>291</v>
+        <v>101</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>292</v>
@@ -2613,26 +2619,26 @@
     </row>
     <row r="142" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B142" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B143" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="C142" s="1" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="B143" s="2" t="s">
-        <v>288</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="1" t="s">
+        <v>298</v>
+      </c>
       <c r="B144" s="2" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>299</v>
@@ -2640,45 +2646,53 @@
     </row>
     <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B145" s="2" t="s">
-        <v>278</v>
+        <v>300</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="1" t="s">
-        <v>301</v>
-      </c>
       <c r="B146" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C146" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="C146" s="1" t="s">
+    </row>
+    <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="1" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B147" s="2" t="s">
-        <v>34</v>
+        <v>304</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>118</v>
+        <v>305</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B148" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>166</v>
+        <v>118</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B149" s="2" t="s">
-        <v>304</v>
+        <v>36</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>305</v>
+        <v>168</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B150" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>307</v>
       </c>
     </row>
   </sheetData>
